--- a/scalability evaluation/input samples/sample_100.xlsx
+++ b/scalability evaluation/input samples/sample_100.xlsx
@@ -442,1001 +442,1001 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6084</v>
+        <v>1624</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Q55902846</t>
+          <t>Q115043621</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5023</v>
+        <v>6760</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Q33198462</t>
+          <t>Q21573510</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5236</v>
+        <v>5421</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Q3909446</t>
+          <t>Q16358809</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7082</v>
+        <v>4344</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Q77877606</t>
+          <t>Q138031795</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3521</v>
+        <v>2673</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Q16191970</t>
+          <t>Q123876853</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>921</v>
+        <v>11365</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Q111064496</t>
+          <t>Q65566564</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1315</v>
+        <v>11631</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Q111139816</t>
+          <t>Q65587517</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7205</v>
+        <v>3473</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Q8063273</t>
+          <t>Q130620130</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4328</v>
+        <v>8887</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Q25443487</t>
+          <t>Q4316586</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6428</v>
+        <v>6520</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Q6275139</t>
+          <t>Q20512914</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6318</v>
+        <v>13016</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Q60042813</t>
+          <t>Q918355</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3628</v>
+        <v>5996</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Q16968899</t>
+          <t>Q18223472</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6882</v>
+        <v>10949</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Q7270937</t>
+          <t>Q63764725</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2003</v>
+        <v>3299</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Q116892857</t>
+          <t>Q12730564</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2519</v>
+        <v>9082</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Q126615575</t>
+          <t>Q45673808</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4477</v>
+        <v>7439</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Q26523974</t>
+          <t>Q27171675</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4290</v>
+        <v>1834</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Q24940016</t>
+          <t>Q116935109</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4392</v>
+        <v>677</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Q26398139</t>
+          <t>Q109119238</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4159</v>
+        <v>2178</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Q22674726</t>
+          <t>Q12208895</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3557</v>
+        <v>1279</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Q16635490</t>
+          <t>Q111904563</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1386</v>
+        <v>1092</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Q111603314</t>
+          <t>Q111229252</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2242</v>
+        <v>6542</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Q122166488</t>
+          <t>Q2059680</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>603</v>
+        <v>2469</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Q110264920</t>
+          <t>Q123716954</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3103</v>
+        <v>7492</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Q138379736</t>
+          <t>Q27915617</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6859</v>
+        <v>3292</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Q7190754</t>
+          <t>Q12726694</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4721</v>
+        <v>5552</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Q2944393</t>
+          <t>Q16828475</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7382</v>
+        <v>1227</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Q945577</t>
+          <t>Q111520230</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>458</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Q100256441</t>
+          <t>Q107161471</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>5136</v>
+        <v>13157</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Q36878905</t>
+          <t>Q953882</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6466</v>
+        <v>2491</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Q64027385</t>
+          <t>Q12384353</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>5544</v>
+        <v>6265</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Q4686584</t>
+          <t>Q1943881</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>7008</v>
+        <v>1698</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Q7611354</t>
+          <t>Q115858535</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>5043</v>
+        <v>2357</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Q3359411</t>
+          <t>Q123699338</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2376</v>
+        <v>223</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Q124514807</t>
+          <t>Q105335900</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>361</v>
+        <v>1617</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Q10715741</t>
+          <t>Q115004764</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>6238</v>
+        <v>3273</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Q58528981</t>
+          <t>Q12713471</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3813</v>
+        <v>11745</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Q1798076</t>
+          <t>Q65597702</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6521</v>
+        <v>6631</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Q6485742</t>
+          <t>Q20900586</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4914</v>
+        <v>4890</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Q30298984</t>
+          <t>Q15616933</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3728</v>
+        <v>3019</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Q17215482</t>
+          <t>Q123898655</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2381</v>
+        <v>8351</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Q124580319</t>
+          <t>Q3324762</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4388</v>
+        <v>9103</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Q26390034</t>
+          <t>Q45781189</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>899</v>
+        <v>527</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Q111063448</t>
+          <t>Q10799296</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1769</v>
+        <v>2697</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Q11509633</t>
+          <t>Q123878841</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2190</v>
+        <v>4010</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Q1207066</t>
+          <t>Q136684903</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>6657</v>
+        <v>8148</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Q67807694</t>
+          <t>Q3102506</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1725</v>
+        <v>762</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Q114625505</t>
+          <t>Q109693047</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>6126</v>
+        <v>1079</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Q5646268</t>
+          <t>Q111228179</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>6484</v>
+        <v>7328</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Q64142452</t>
+          <t>Q26266078</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>512</v>
+        <v>9439</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Q109366822</t>
+          <t>Q50772064</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>6552</v>
+        <v>10661</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Q65344002</t>
+          <t>Q61892688</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>6890</v>
+        <v>269</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Q7280957</t>
+          <t>Q105724263</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2772</v>
+        <v>8553</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Q131947859</t>
+          <t>Q3620345</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>5723</v>
+        <v>1176</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Q5029772</t>
+          <t>Q111323386</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2708</v>
+        <v>11769</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Q131188907</t>
+          <t>Q65601540</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>515</v>
+        <v>9390</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Q109366991</t>
+          <t>Q4990369</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2443</v>
+        <v>2912</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Q125502353</t>
+          <t>Q123892620</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>6121</v>
+        <v>7595</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Q5641355</t>
+          <t>Q2843930</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1210</v>
+        <v>6822</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Q111121137</t>
+          <t>Q21857231</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2046</v>
+        <v>2608</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Q117012215</t>
+          <t>Q123873227</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>7333</v>
+        <v>6368</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Q90257416</t>
+          <t>Q19849412</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>5836</v>
+        <v>6519</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Q52860124</t>
+          <t>Q20508530</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>3393</v>
+        <v>4372</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Q14714276</t>
+          <t>Q138033123</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>6142</v>
+        <v>313</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Q56583910</t>
+          <t>Q106147927</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>7448</v>
+        <v>13536</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Q97309712</t>
+          <t>Q98258994</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1668</v>
+        <v>748</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Q11391792</t>
+          <t>Q109602548</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>6924</v>
+        <v>4215</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Q738421</t>
+          <t>Q137696296</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>3140</v>
+        <v>8749</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Q138668299</t>
+          <t>Q4054450</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>5543</v>
+        <v>6554</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Q4686512</t>
+          <t>Q20630564</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>7114</v>
+        <v>1643</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Q7885403</t>
+          <t>Q11530414</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>6758</v>
+        <v>1886</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Q6886654</t>
+          <t>Q11737907</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>3736</v>
+        <v>8972</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Q17220150</t>
+          <t>Q4456383</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>3577</v>
+        <v>10203</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Q16824882</t>
+          <t>Q5896166</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1125</v>
+        <v>4544</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Q111111288</t>
+          <t>Q138760227</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>243</v>
+        <v>13132</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Q106351484</t>
+          <t>Q94841132</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1872</v>
+        <v>1304</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Q115966932</t>
+          <t>Q112078439</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>303</v>
+        <v>10580</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Q106829967</t>
+          <t>Q61653554</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1297</v>
+        <v>3121</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Q111138794</t>
+          <t>Q124971152</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>5545</v>
+        <v>3553</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Q4686685</t>
+          <t>Q1313183</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>273</v>
+        <v>9023</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Q106614483</t>
+          <t>Q454424</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>436</v>
+        <v>2348</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Q108169104</t>
+          <t>Q12363921</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1266</v>
+        <v>1048</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Q111126479</t>
+          <t>Q111180215</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>5030</v>
+        <v>80</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Q3330733</t>
+          <t>Q10311282</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>3623</v>
+        <v>4139</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Q16961275</t>
+          <t>Q137680770</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1317</v>
+        <v>2537</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Q111139866</t>
+          <t>Q123868477</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>4724</v>
+        <v>11492</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Q29507996</t>
+          <t>Q65577510</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>4890</v>
+        <v>6241</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Q30297294</t>
+          <t>Q19300384</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1838</v>
+        <v>3226</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Q115650287</t>
+          <t>Q126365222</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2372</v>
+        <v>1803</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Q124514378</t>
+          <t>Q116931884</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>7358</v>
+        <v>4672</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Q918046</t>
+          <t>Q14430</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1782</v>
+        <v>9785</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Q11519211</t>
+          <t>Q5490860</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2814</v>
+        <v>5242</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Q133308002</t>
+          <t>Q16093533</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2285</v>
+        <v>3171</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Q122974235</t>
+          <t>Q125780387</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>6287</v>
+        <v>1029</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Q5920774</t>
+          <t>Q111176717</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1366</v>
+        <v>5467</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Q111398794</t>
+          <t>Q16576929</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>6031</v>
+        <v>9817</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Q5505987</t>
+          <t>Q55124800</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>6698</v>
+        <v>4527</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Q67812488</t>
+          <t>Q138759114</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>3900</v>
+        <v>8728</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Q1881178</t>
+          <t>Q3953110</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>4583</v>
+        <v>5462</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Q2702274</t>
+          <t>Q16566847</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>968</v>
+        <v>13447</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Q111067794</t>
+          <t>Q98247186</t>
         </is>
       </c>
     </row>
